--- a/data/trans_camb/P2A_senso_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_senso_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 2,06</t>
+          <t>-1,32; 2,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,77; -0,07</t>
+          <t>-2,69; -0,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,59</t>
+          <t>-1,46; 1,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 3,15</t>
+          <t>0,02; 2,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,96</t>
+          <t>-1,31; 0,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,5</t>
+          <t>-0,19; 2,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,96</t>
+          <t>-0,25; 1,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,04</t>
+          <t>-1,75; 0,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,45</t>
+          <t>-0,5; 1,6</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-47,39; 129,67</t>
+          <t>-46,34; 134,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-87,77; 8,1</t>
+          <t>-86,47; -0,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-56,76; 121,02</t>
+          <t>-51,93; 108,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 485,76</t>
+          <t>-13,51; 457,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-75,48; 182,52</t>
+          <t>-72,15; 157,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,61; 402,34</t>
+          <t>-18,56; 393,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 153,58</t>
+          <t>-13,21; 156,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-71,43; 10,05</t>
+          <t>-74,59; 7,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-26,81; 111,78</t>
+          <t>-28,6; 126,47</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,38</t>
+          <t>-1,12; 1,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,54</t>
+          <t>-1,62; 0,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 1,86</t>
+          <t>-1,15; 1,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,55</t>
+          <t>-0,96; 1,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,62</t>
+          <t>-1,55; 0,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,54</t>
+          <t>0,16; 2,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,14</t>
+          <t>-0,51; 1,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,22</t>
+          <t>-1,27; 0,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 1,75</t>
+          <t>-0,22; 1,77</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-51,79; 157,56</t>
+          <t>-56,48; 153,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-74,25; 78,25</t>
+          <t>-78,69; 65,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-49,07; 187,5</t>
+          <t>-52,06; 179,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,28; 142,39</t>
+          <t>-42,44; 123,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,13; 64,26</t>
+          <t>-69,7; 57,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 213,57</t>
+          <t>3,57; 217,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,92; 94,07</t>
+          <t>-25,84; 101,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,27; 23,38</t>
+          <t>-63,53; 29,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 149,07</t>
+          <t>-11,05; 151,26</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,11</t>
+          <t>-1,3; 1,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,99</t>
+          <t>-1,47; 0,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,98</t>
+          <t>0,78; 3,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,28</t>
+          <t>-1,44; 1,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,31</t>
+          <t>-2,04; 0,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 55,36</t>
+          <t>2,11; 60,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,74</t>
+          <t>-1,03; 0,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,37</t>
+          <t>-1,34; 0,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 41,38</t>
+          <t>2,13; 40,07</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-73,78; 250,45</t>
+          <t>-77,62; 238,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-82,42; 174,67</t>
+          <t>-81,48; 212,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,43; 740,98</t>
+          <t>29,91; 728,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-66,68; 155,67</t>
+          <t>-65,97; 134,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-83,87; 49,78</t>
+          <t>-84,7; 37,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>111,06; 7872,46</t>
+          <t>117,33; 9348,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-54,67; 82,38</t>
+          <t>-56,96; 92,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,23; 51,54</t>
+          <t>-71,75; 43,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>144,73; 4912,44</t>
+          <t>137,96; 5007,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,46</t>
+          <t>-0,99; 1,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,9</t>
+          <t>-1,18; 1,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,4</t>
+          <t>-0,79; 1,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,07</t>
+          <t>-0,55; 2,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,08</t>
+          <t>-1,94; 0,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,6</t>
+          <t>-0,77; 1,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,4</t>
+          <t>-0,34; 1,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,23</t>
+          <t>-1,28; 0,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,2</t>
+          <t>-0,45; 1,22</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-48,02; 143,23</t>
+          <t>-54,39; 149,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-63,39; 101,87</t>
+          <t>-64,17; 131,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-47,27; 135,02</t>
+          <t>-43,28; 158,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,65; 155,79</t>
+          <t>-22,81; 171,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-76,86; 15,69</t>
+          <t>-75,15; 31,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,18; 116,16</t>
+          <t>-29,34; 105,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-20,43; 111,38</t>
+          <t>-18,3; 97,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-60,15; 21,1</t>
+          <t>-59,53; 18,82</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-22,69; 95,84</t>
+          <t>-20,7; 93,84</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,73</t>
+          <t>-0,52; 0,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,05</t>
+          <t>-1,06; 0,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,35</t>
+          <t>-0,06; 1,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,18</t>
+          <t>-0,12; 1,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; -0,07</t>
+          <t>-1,19; -0,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,09; 23,6</t>
+          <t>1,05; 23,53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 0,84</t>
+          <t>-0,08; 0,82</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; -0,17</t>
+          <t>-0,95; -0,14</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,86; 13,82</t>
+          <t>0,83; 12,91</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-29,95; 58,24</t>
+          <t>-28,62; 60,0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-60,36; 7,22</t>
+          <t>-58,53; 6,72</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 102,16</t>
+          <t>-4,75; 110,05</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 84,94</t>
+          <t>-6,61; 88,45</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-57,67; -3,42</t>
+          <t>-60,19; -1,67</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,71; 1450,72</t>
+          <t>59,89; 1696,84</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 57,42</t>
+          <t>-5,28; 58,05</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-54,1; -12,03</t>
+          <t>-50,91; -7,29</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>53,77; 918,72</t>
+          <t>51,28; 850,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_senso_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_senso_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>-0,19</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>1,39</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,61</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 2,07</t>
+          <t>-1,44; 2,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,69; -0,14</t>
+          <t>-2,8; -0,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,69</t>
+          <t>-1,75; 1,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 2,97</t>
+          <t>-0,15; 2,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,9</t>
+          <t>-1,31; 0,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 2,47</t>
+          <t>0,21; 2,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,96</t>
+          <t>-0,18; 2,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,01</t>
+          <t>-1,62; 0,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,6</t>
+          <t>-0,45; 1,69</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-1,35%</t>
+          <t>-8,3%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>116,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>35,38%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-46,34; 134,15</t>
+          <t>-46,85; 144,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-86,47; -0,51</t>
+          <t>-86,7; 3,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-51,93; 108,37</t>
+          <t>-57,72; 96,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 457,48</t>
+          <t>-19,37; 401,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-72,15; 157,27</t>
+          <t>-76,57; 145,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,56; 393,39</t>
+          <t>-2,7; 421,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 156,66</t>
+          <t>-11,68; 158,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-74,59; 7,52</t>
+          <t>-72,42; 5,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-28,6; 126,47</t>
+          <t>-22,47; 130,36</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>1,14</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,32</t>
+          <t>-1,04; 1,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,51</t>
+          <t>-1,57; 0,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 1,78</t>
+          <t>-0,45; 2,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,42</t>
+          <t>-0,91; 1,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,61</t>
+          <t>-1,59; 0,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 2,47</t>
+          <t>0,05; 2,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,17</t>
+          <t>-0,63; 1,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,31</t>
+          <t>-1,29; 0,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 1,77</t>
+          <t>0,2; 2,01</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>71,43%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-56,48; 153,69</t>
+          <t>-51,78; 140,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-78,69; 65,31</t>
+          <t>-76,94; 72,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-52,06; 179,87</t>
+          <t>-27,55; 233,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-42,44; 123,42</t>
+          <t>-41,79; 157,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,7; 57,16</t>
+          <t>-70,11; 66,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 217,29</t>
+          <t>-0,42; 212,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,84; 101,08</t>
+          <t>-32,66; 93,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,53; 29,43</t>
+          <t>-62,42; 20,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 151,26</t>
+          <t>7,03; 169,86</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,29</t>
+          <t>2,85</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,69</t>
+          <t>3,18</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14,52</t>
+          <t>3,01</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,14</t>
+          <t>-1,27; 1,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1119,37 +1119,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,97</t>
+          <t>1,22; 4,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,2</t>
+          <t>-1,32; 1,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,27</t>
+          <t>-2,02; 0,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 60,04</t>
+          <t>1,54; 4,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,81</t>
+          <t>-0,9; 0,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,36</t>
+          <t>-1,36; 0,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 40,07</t>
+          <t>1,92; 4,3</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>197,06%</t>
+          <t>244,52%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1494,3%</t>
+          <t>200,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1055,22%</t>
+          <t>219,14%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-77,62; 238,39</t>
+          <t>-74,63; 225,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-81,48; 212,94</t>
+          <t>-84,32; 217,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,91; 728,7</t>
+          <t>48,32; 749,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-65,97; 134,33</t>
+          <t>-62,92; 120,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-84,7; 37,34</t>
+          <t>-83,01; 62,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>117,33; 9348,8</t>
+          <t>55,54; 477,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-56,96; 92,89</t>
+          <t>-53,17; 100,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-71,75; 43,23</t>
+          <t>-72,47; 49,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>137,96; 5007,11</t>
+          <t>99,07; 466,09</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,52</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,3</t>
+          <t>-0,87; 1,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,07</t>
+          <t>-1,19; 0,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,39</t>
+          <t>-0,77; 1,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,13</t>
+          <t>-0,65; 2,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,21</t>
+          <t>-1,96; 0,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 1,46</t>
+          <t>-0,4; 1,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,29</t>
+          <t>-0,41; 1,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,22</t>
+          <t>-1,32; 0,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,22</t>
+          <t>-0,26; 1,32</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>31,0%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-54,39; 149,29</t>
+          <t>-49,0; 167,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-64,17; 131,28</t>
+          <t>-62,99; 117,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-43,28; 158,17</t>
+          <t>-38,3; 180,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-22,81; 171,65</t>
+          <t>-27,17; 159,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-75,15; 31,48</t>
+          <t>-74,89; 17,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-29,34; 105,84</t>
+          <t>-17,05; 137,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,3; 97,94</t>
+          <t>-21,03; 98,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-59,53; 18,82</t>
+          <t>-60,47; 19,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-20,7; 93,84</t>
+          <t>-12,45; 107,69</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,62</t>
+          <t>1,57</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,75</t>
+          <t>1,27</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,74</t>
+          <t>-0,48; 0,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,05</t>
+          <t>-1,12; 0,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,4</t>
+          <t>0,3; 1,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,22</t>
+          <t>-0,16; 1,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; -0,03</t>
+          <t>-1,19; -0,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 23,53</t>
+          <t>0,93; 2,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 0,82</t>
+          <t>-0,12; 0,82</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; -0,14</t>
+          <t>-0,98; -0,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,83; 12,91</t>
+          <t>0,79; 1,77</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>399,6%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>234,06%</t>
+          <t>79,01%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,62; 60,0</t>
+          <t>-27,2; 62,78</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-58,53; 6,72</t>
+          <t>-59,67; 9,78</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 110,05</t>
+          <t>13,82; 125,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 88,45</t>
+          <t>-8,45; 84,98</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-60,19; -1,67</t>
+          <t>-59,14; -3,13</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,89; 1696,84</t>
+          <t>44,78; 162,34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 58,05</t>
+          <t>-6,74; 58,11</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-50,91; -7,29</t>
+          <t>-53,75; -12,07</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>51,28; 850,91</t>
+          <t>40,46; 125,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_senso_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_senso_R-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad sensorial</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
